--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/sarf_malzeme.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/sarf_malzeme.xlsx
@@ -713,12 +713,12 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>6 ₺/kg</t>
+          <t>6 €/kg</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>6,00 ₺/yıl</t>
+          <t>6,00 €/yıl</t>
         </is>
       </c>
     </row>
@@ -740,12 +740,12 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>4 ₺/lt</t>
+          <t>4 €/lt</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>29,60 ₺/yıl</t>
+          <t>29,60 €/yıl</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       <c r="D7" s="17" t="n"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>35,60 ₺/yıl</t>
+          <t>35,60 €/yıl</t>
         </is>
       </c>
     </row>
